--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
@@ -1211,7 +1211,7 @@
         <v>28</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
         <v>17</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
         <v>19</v>
       </c>
       <c r="I41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3275,7 +3275,7 @@
         <v>31</v>
       </c>
       <c r="I66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
@@ -1214,7 +1214,7 @@
         <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
         <v>14</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
@@ -1211,10 +1211,10 @@
         <v>28</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
         <v>17</v>
       </c>
       <c r="I32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
         <v>19</v>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3275,10 +3275,10 @@
         <v>31</v>
       </c>
       <c r="I66" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
@@ -569,7 +569,7 @@
         <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1211,10 +1211,10 @@
         <v>28</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
         <v>17</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2200,10 +2200,10 @@
         <v>19</v>
       </c>
       <c r="I41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
         <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -3275,10 +3275,10 @@
         <v>31</v>
       </c>
       <c r="I66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
@@ -569,7 +569,7 @@
         <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1214,7 +1214,7 @@
         <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1816,7 +1816,7 @@
         <v>8</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
         <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
         <v>14</v>
       </c>
       <c r="J66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
@@ -569,7 +569,7 @@
         <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
         <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1214,7 +1214,7 @@
         <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>8</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
         <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
         <v>14</v>
       </c>
       <c r="J66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Birds/heatmap.xlsx
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2375,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2977,7 +2977,7 @@
         <v>2</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -3020,7 +3020,7 @@
         <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
